--- a/docs/downloads/kosdaq_long_short_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_history.xlsx
@@ -495,10 +495,10 @@
         <v>11600</v>
       </c>
       <c r="F2" t="n">
-        <v>8621</v>
+        <v>8620</v>
       </c>
       <c r="G2" t="n">
-        <v>100003600</v>
+        <v>99992000</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -559,10 +559,10 @@
         <v>93300</v>
       </c>
       <c r="F4" t="n">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G4" t="n">
-        <v>100017600</v>
+        <v>99924300</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -591,10 +591,10 @@
         <v>35550</v>
       </c>
       <c r="F5" t="n">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="G5" t="n">
-        <v>100002150</v>
+        <v>99966600</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -655,10 +655,10 @@
         <v>10920</v>
       </c>
       <c r="F7" t="n">
-        <v>9158</v>
+        <v>9157</v>
       </c>
       <c r="G7" t="n">
-        <v>100005360</v>
+        <v>99994440</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -687,10 +687,10 @@
         <v>22250</v>
       </c>
       <c r="F8" t="n">
-        <v>6742</v>
+        <v>6741</v>
       </c>
       <c r="G8" t="n">
-        <v>150009500</v>
+        <v>149987250</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -751,10 +751,10 @@
         <v>56500</v>
       </c>
       <c r="F10" t="n">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="G10" t="n">
-        <v>100005000</v>
+        <v>99948500</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -815,10 +815,10 @@
         <v>35900</v>
       </c>
       <c r="F12" t="n">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="G12" t="n">
-        <v>100017400</v>
+        <v>99981500</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -943,10 +943,10 @@
         <v>426000</v>
       </c>
       <c r="F16" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G16" t="n">
-        <v>100110000</v>
+        <v>99684000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -975,10 +975,10 @@
         <v>105200</v>
       </c>
       <c r="F17" t="n">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G17" t="n">
-        <v>100045200</v>
+        <v>99940000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1007,10 +1007,10 @@
         <v>54200</v>
       </c>
       <c r="F18" t="n">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="G18" t="n">
-        <v>150025600</v>
+        <v>149971400</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1103,10 +1103,10 @@
         <v>8320</v>
       </c>
       <c r="F21" t="n">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="G21" t="n">
-        <v>50003200</v>
+        <v>49994880</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>

--- a/docs/downloads/kosdaq_long_short_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,145 +473,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>와이지-원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>019210</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11600</v>
+        <v>14260</v>
       </c>
       <c r="F2" t="n">
-        <v>8620</v>
+        <v>3510</v>
       </c>
       <c r="G2" t="n">
-        <v>99992000</v>
+        <v>50052600</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>030530</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18020</v>
+        <v>22500</v>
       </c>
       <c r="F3" t="n">
-        <v>5549</v>
+        <v>4449</v>
       </c>
       <c r="G3" t="n">
-        <v>99992980</v>
+        <v>100102500</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>032820</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 확대(숏)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>93300</v>
+        <v>10630</v>
       </c>
       <c r="F4" t="n">
-        <v>1071</v>
+        <v>798</v>
       </c>
       <c r="G4" t="n">
-        <v>99924300</v>
+        <v>8482740</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>35550</v>
+        <v>17160</v>
       </c>
       <c r="F5" t="n">
-        <v>2812</v>
+        <v>5549</v>
       </c>
       <c r="G5" t="n">
-        <v>99966600</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>95220840</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-4.77</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,30 +622,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>62800</v>
+        <v>10200</v>
       </c>
       <c r="F6" t="n">
-        <v>1592</v>
+        <v>4908</v>
       </c>
       <c r="G6" t="n">
-        <v>99977600</v>
+        <v>50061600</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,30 +654,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10920</v>
+        <v>19630</v>
       </c>
       <c r="F7" t="n">
-        <v>9157</v>
+        <v>2550</v>
       </c>
       <c r="G7" t="n">
-        <v>99994440</v>
+        <v>50056500</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,254 +686,260 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>22250</v>
+        <v>66600</v>
       </c>
       <c r="F8" t="n">
-        <v>6741</v>
+        <v>1503</v>
       </c>
       <c r="G8" t="n">
-        <v>149987250</v>
+        <v>100099800</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>23450</v>
+        <v>94200</v>
       </c>
       <c r="F9" t="n">
-        <v>4264</v>
+        <v>540</v>
       </c>
       <c r="G9" t="n">
-        <v>99990800</v>
+        <v>50868000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>56500</v>
+        <v>34850</v>
       </c>
       <c r="F10" t="n">
-        <v>1769</v>
+        <v>2812</v>
       </c>
       <c r="G10" t="n">
-        <v>99948500</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>97998200</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>33600</v>
+        <v>60000</v>
       </c>
       <c r="F11" t="n">
-        <v>1488</v>
+        <v>1592</v>
       </c>
       <c r="G11" t="n">
-        <v>49996800</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>95520000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.46</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>35900</v>
+        <v>11330</v>
       </c>
       <c r="F12" t="n">
-        <v>2785</v>
+        <v>9157</v>
       </c>
       <c r="G12" t="n">
-        <v>99981500</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>103748810</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.75</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9350</v>
+        <v>21600</v>
       </c>
       <c r="F13" t="n">
-        <v>10695</v>
+        <v>2529</v>
       </c>
       <c r="G13" t="n">
-        <v>99998250</v>
+        <v>54626400</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>307500</v>
+        <v>22200</v>
       </c>
       <c r="F14" t="n">
-        <v>325</v>
+        <v>246</v>
       </c>
       <c r="G14" t="n">
-        <v>99937500</v>
+        <v>5461200</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>휴메딕스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>200670</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 확대(숏)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>26150</v>
+        <v>52800</v>
       </c>
       <c r="F15" t="n">
-        <v>3824</v>
+        <v>127</v>
       </c>
       <c r="G15" t="n">
-        <v>99997600</v>
+        <v>6705600</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -940,175 +948,1243 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>426000</v>
+        <v>20650</v>
       </c>
       <c r="F16" t="n">
-        <v>234</v>
+        <v>2424</v>
       </c>
       <c r="G16" t="n">
-        <v>99684000</v>
+        <v>50055600</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105200</v>
+        <v>31900</v>
       </c>
       <c r="F17" t="n">
-        <v>950</v>
+        <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>99940000</v>
+        <v>2583900</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>098460</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>54200</v>
+        <v>27900</v>
       </c>
       <c r="F18" t="n">
-        <v>2767</v>
+        <v>3588</v>
       </c>
       <c r="G18" t="n">
-        <v>149971400</v>
+        <v>100105200</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>127700</v>
+        <v>35650</v>
       </c>
       <c r="F19" t="n">
-        <v>783</v>
+        <v>2785</v>
       </c>
       <c r="G19" t="n">
-        <v>99989100</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>99285250</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>425420</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>46250</v>
+        <v>8760</v>
       </c>
       <c r="F20" t="n">
-        <v>2162</v>
+        <v>10695</v>
       </c>
       <c r="G20" t="n">
-        <v>99992500</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>93688200</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.31</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>288500</v>
+      </c>
+      <c r="F21" t="n">
+        <v>152</v>
+      </c>
+      <c r="G21" t="n">
+        <v>43852000</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>휴메딕스</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>200670</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>25850</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3824</v>
+      </c>
+      <c r="G22" t="n">
+        <v>98850400</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>386500</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>90441000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-9.27</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>타이거일렉</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>219130</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>60400</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1657</v>
+      </c>
+      <c r="G24" t="n">
+        <v>100082800</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>226950</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>95900</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1044</v>
+      </c>
+      <c r="G25" t="n">
+        <v>100119600</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>101200</v>
+      </c>
+      <c r="F26" t="n">
+        <v>39</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3946800</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>114800</v>
+      </c>
+      <c r="F27" t="n">
+        <v>872</v>
+      </c>
+      <c r="G27" t="n">
+        <v>100105600</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>682</v>
+      </c>
+      <c r="G28" t="n">
+        <v>32736000</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>319660</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>126500</v>
+      </c>
+      <c r="F29" t="n">
+        <v>783</v>
+      </c>
+      <c r="G29" t="n">
+        <v>99049500</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>루닛</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>328130</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F30" t="n">
+        <v>11124</v>
+      </c>
+      <c r="G30" t="n">
+        <v>100116000</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>425420</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>52700</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2162</v>
+      </c>
+      <c r="G31" t="n">
+        <v>113937400</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-13.95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>마녀공장</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>439090</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>16010</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6253</v>
+      </c>
+      <c r="G32" t="n">
+        <v>100110530</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>파인엠텍</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>441270</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>9350</v>
+      </c>
+      <c r="F33" t="n">
+        <v>655</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6124250</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>475830</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>55900</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1791</v>
+      </c>
+      <c r="G34" t="n">
+        <v>100116900</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>우리기술</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>032820</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>11600</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8620</v>
+      </c>
+      <c r="G35" t="n">
+        <v>99992000</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>동성화인텍</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>033500</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>18020</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5549</v>
+      </c>
+      <c r="G36" t="n">
+        <v>99992980</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>058610</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>93300</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1071</v>
+      </c>
+      <c r="G37" t="n">
+        <v>99924300</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>067310</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>35550</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2812</v>
+      </c>
+      <c r="G38" t="n">
+        <v>99966600</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>비에이치아이</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>083650</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>62800</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1592</v>
+      </c>
+      <c r="G39" t="n">
+        <v>99977600</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>유니테스트</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>086390</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>10920</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9157</v>
+      </c>
+      <c r="G40" t="n">
+        <v>99994440</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>086450</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>22250</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6741</v>
+      </c>
+      <c r="G41" t="n">
+        <v>149987250</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>23450</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4264</v>
+      </c>
+      <c r="G42" t="n">
+        <v>99990800</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>56500</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1769</v>
+      </c>
+      <c r="G43" t="n">
+        <v>99948500</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>씨젠</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>096530</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>33600</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1488</v>
+      </c>
+      <c r="G44" t="n">
+        <v>49996800</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>35900</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2785</v>
+      </c>
+      <c r="G45" t="n">
+        <v>99981500</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>144960</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>9350</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10695</v>
+      </c>
+      <c r="G46" t="n">
+        <v>99998250</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>307500</v>
+      </c>
+      <c r="F47" t="n">
+        <v>325</v>
+      </c>
+      <c r="G47" t="n">
+        <v>99937500</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>휴메딕스</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>200670</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>26150</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3824</v>
+      </c>
+      <c r="G48" t="n">
+        <v>99997600</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>426000</v>
+      </c>
+      <c r="F49" t="n">
+        <v>234</v>
+      </c>
+      <c r="G49" t="n">
+        <v>99684000</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>105200</v>
+      </c>
+      <c r="F50" t="n">
+        <v>950</v>
+      </c>
+      <c r="G50" t="n">
+        <v>99940000</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2767</v>
+      </c>
+      <c r="G51" t="n">
+        <v>149971400</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>319660</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>127700</v>
+      </c>
+      <c r="F52" t="n">
+        <v>783</v>
+      </c>
+      <c r="G52" t="n">
+        <v>99989100</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>425420</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>46250</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2162</v>
+      </c>
+      <c r="G53" t="n">
+        <v>99992500</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>파인엠텍</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>441270</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E54" t="n">
         <v>8320</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F54" t="n">
         <v>6009</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G54" t="n">
         <v>49994880</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,113 +473,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>와이지-원</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>019210</t>
+          <t>0011A0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14260</v>
+        <v>11110</v>
       </c>
       <c r="F2" t="n">
-        <v>3510</v>
+        <v>4283</v>
       </c>
       <c r="G2" t="n">
-        <v>50052600</v>
+        <v>47584130</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>와이지-원</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>019210</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22500</v>
+        <v>13620</v>
       </c>
       <c r="F3" t="n">
-        <v>4449</v>
+        <v>3510</v>
       </c>
       <c r="G3" t="n">
-        <v>100102500</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>47806200</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-4.49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>030530</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10630</v>
+        <v>22550</v>
       </c>
       <c r="F4" t="n">
-        <v>798</v>
+        <v>4449</v>
       </c>
       <c r="G4" t="n">
-        <v>8482740</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>100324950</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>032820</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,22 +592,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17160</v>
+        <v>11810</v>
       </c>
       <c r="F5" t="n">
-        <v>5549</v>
+        <v>9418</v>
       </c>
       <c r="G5" t="n">
-        <v>95220840</v>
+        <v>111226580</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.77</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,66 +622,66 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 확대(숏)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10200</v>
+        <v>7870</v>
       </c>
       <c r="F6" t="n">
-        <v>4908</v>
+        <v>1139</v>
       </c>
       <c r="G6" t="n">
-        <v>50061600</v>
+        <v>8963930</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>세종텔레콤</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>036630</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19630</v>
+        <v>9370</v>
       </c>
       <c r="F7" t="n">
-        <v>2550</v>
+        <v>5079</v>
       </c>
       <c r="G7" t="n">
-        <v>50056500</v>
+        <v>47590230</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -686,96 +690,94 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>66600</v>
+        <v>25050</v>
       </c>
       <c r="F8" t="n">
-        <v>1503</v>
+        <v>3799</v>
       </c>
       <c r="G8" t="n">
-        <v>100099800</v>
+        <v>95164950</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>94200</v>
+        <v>194600</v>
       </c>
       <c r="F9" t="n">
-        <v>540</v>
+        <v>245</v>
       </c>
       <c r="G9" t="n">
-        <v>50868000</v>
+        <v>47677000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>YTN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>040300</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>34850</v>
+        <v>1993</v>
       </c>
       <c r="F10" t="n">
-        <v>2812</v>
+        <v>9551</v>
       </c>
       <c r="G10" t="n">
-        <v>97998200</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.97</v>
-      </c>
+        <v>19035143</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,326 +786,322 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>60000</v>
+        <v>21200</v>
       </c>
       <c r="F11" t="n">
-        <v>1592</v>
+        <v>2550</v>
       </c>
       <c r="G11" t="n">
-        <v>95520000</v>
+        <v>54060000</v>
       </c>
       <c r="H11" t="n">
-        <v>4.46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>11330</v>
+        <v>68900</v>
       </c>
       <c r="F12" t="n">
-        <v>9157</v>
+        <v>260</v>
       </c>
       <c r="G12" t="n">
-        <v>103748810</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.75</v>
-      </c>
+        <v>17914000</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21600</v>
+        <v>91300</v>
       </c>
       <c r="F13" t="n">
-        <v>2529</v>
+        <v>531</v>
       </c>
       <c r="G13" t="n">
-        <v>54626400</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>48480300</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>22200</v>
+        <v>91300</v>
       </c>
       <c r="F14" t="n">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="G14" t="n">
-        <v>5461200</v>
+        <v>18990400</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>52800</v>
+        <v>19930</v>
       </c>
       <c r="F15" t="n">
-        <v>127</v>
+        <v>7360</v>
       </c>
       <c r="G15" t="n">
-        <v>6705600</v>
+        <v>146684800</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>20650</v>
+        <v>22500</v>
       </c>
       <c r="F16" t="n">
-        <v>2424</v>
+        <v>1972</v>
       </c>
       <c r="G16" t="n">
-        <v>50055600</v>
+        <v>44370000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>31900</v>
+        <v>51100</v>
       </c>
       <c r="F17" t="n">
-        <v>81</v>
+        <v>592</v>
       </c>
       <c r="G17" t="n">
-        <v>2583900</v>
+        <v>30251200</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>27900</v>
+        <v>20550</v>
       </c>
       <c r="F18" t="n">
-        <v>3588</v>
+        <v>108</v>
       </c>
       <c r="G18" t="n">
-        <v>100105200</v>
+        <v>2219400</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>케이아이엔엑스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>093320</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>35650</v>
+        <v>139000</v>
       </c>
       <c r="F19" t="n">
-        <v>2785</v>
+        <v>411</v>
       </c>
       <c r="G19" t="n">
-        <v>99285250</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.7</v>
-      </c>
+        <v>57129000</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8760</v>
+        <v>31450</v>
       </c>
       <c r="F20" t="n">
-        <v>10695</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>93688200</v>
-      </c>
-      <c r="H20" t="n">
-        <v>6.31</v>
-      </c>
+        <v>1761200</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>098460</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1112,130 +1110,126 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>288500</v>
+        <v>27150</v>
       </c>
       <c r="F21" t="n">
-        <v>152</v>
+        <v>784</v>
       </c>
       <c r="G21" t="n">
-        <v>43852000</v>
+        <v>21285600</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>휴메딕스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>200670</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>25850</v>
+        <v>41300</v>
       </c>
       <c r="F22" t="n">
-        <v>3824</v>
+        <v>1152</v>
       </c>
       <c r="G22" t="n">
-        <v>98850400</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.15</v>
-      </c>
+        <v>47577600</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>386500</v>
+        <v>284000</v>
       </c>
       <c r="F23" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G23" t="n">
-        <v>90441000</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-9.27</v>
-      </c>
+        <v>66740000</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>60400</v>
+        <v>21100</v>
       </c>
       <c r="F24" t="n">
-        <v>1657</v>
+        <v>902</v>
       </c>
       <c r="G24" t="n">
-        <v>100082800</v>
+        <v>19032200</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>큐브엔터</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>226950</t>
+          <t>182360</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1244,30 +1238,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>95900</v>
+        <v>6110</v>
       </c>
       <c r="F25" t="n">
-        <v>1044</v>
+        <v>4673</v>
       </c>
       <c r="G25" t="n">
-        <v>100119600</v>
+        <v>28552030</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1276,30 +1270,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101200</v>
+        <v>277000</v>
       </c>
       <c r="F26" t="n">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="G26" t="n">
-        <v>3946800</v>
+        <v>28254000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1308,30 +1302,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>114800</v>
+        <v>369000</v>
       </c>
       <c r="F27" t="n">
-        <v>872</v>
+        <v>129</v>
       </c>
       <c r="G27" t="n">
-        <v>100105600</v>
+        <v>47601000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1340,354 +1334,352 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>48000</v>
+        <v>62300</v>
       </c>
       <c r="F28" t="n">
-        <v>682</v>
+        <v>435</v>
       </c>
       <c r="G28" t="n">
-        <v>32736000</v>
+        <v>27100500</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>226950</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>126500</v>
+        <v>99100</v>
       </c>
       <c r="F29" t="n">
-        <v>783</v>
+        <v>372</v>
       </c>
       <c r="G29" t="n">
-        <v>99049500</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+        <v>36865200</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9000</v>
+        <v>91900</v>
       </c>
       <c r="F30" t="n">
-        <v>11124</v>
+        <v>471</v>
       </c>
       <c r="G30" t="n">
-        <v>100116000</v>
+        <v>43284900</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>425420</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>52700</v>
+        <v>115800</v>
       </c>
       <c r="F31" t="n">
-        <v>2162</v>
+        <v>379</v>
       </c>
       <c r="G31" t="n">
-        <v>113937400</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-13.95</v>
-      </c>
+        <v>43888200</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>마녀공장</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>439090</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>16010</v>
+        <v>46250</v>
       </c>
       <c r="F32" t="n">
-        <v>6253</v>
+        <v>1673</v>
       </c>
       <c r="G32" t="n">
-        <v>100110530</v>
+        <v>77376250</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>290720</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>9350</v>
+        <v>2710</v>
       </c>
       <c r="F33" t="n">
-        <v>655</v>
+        <v>14048</v>
       </c>
       <c r="G33" t="n">
-        <v>6124250</v>
+        <v>38070080</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>475830</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>55900</v>
+        <v>34500</v>
       </c>
       <c r="F34" t="n">
-        <v>1791</v>
+        <v>828</v>
       </c>
       <c r="G34" t="n">
-        <v>100116900</v>
+        <v>28566000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>328130</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>11600</v>
+        <v>8700</v>
       </c>
       <c r="F35" t="n">
-        <v>8620</v>
+        <v>2372</v>
       </c>
       <c r="G35" t="n">
-        <v>99992000</v>
+        <v>20636400</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>워트</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>396470</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>18020</v>
+        <v>6630</v>
       </c>
       <c r="F36" t="n">
-        <v>5549</v>
+        <v>7178</v>
       </c>
       <c r="G36" t="n">
-        <v>99992980</v>
+        <v>47590140</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>마녀공장</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>439090</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>93300</v>
+        <v>15890</v>
       </c>
       <c r="F37" t="n">
-        <v>1071</v>
+        <v>2659</v>
       </c>
       <c r="G37" t="n">
-        <v>99924300</v>
+        <v>42251510</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>35550</v>
+        <v>8070</v>
       </c>
       <c r="F38" t="n">
-        <v>2812</v>
+        <v>5354</v>
       </c>
       <c r="G38" t="n">
-        <v>99966600</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>43206780</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>엔젤로보틱스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>455900</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1696,126 +1688,126 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>62800</v>
+        <v>21300</v>
       </c>
       <c r="F39" t="n">
-        <v>1592</v>
+        <v>1787</v>
       </c>
       <c r="G39" t="n">
-        <v>99977600</v>
+        <v>38063100</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에스오에스랩</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>464080</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10920</v>
+        <v>9980</v>
       </c>
       <c r="F40" t="n">
-        <v>9157</v>
+        <v>4768</v>
       </c>
       <c r="G40" t="n">
-        <v>99994440</v>
+        <v>47584640</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>475830</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>22250</v>
+        <v>53000</v>
       </c>
       <c r="F41" t="n">
-        <v>6741</v>
+        <v>354</v>
       </c>
       <c r="G41" t="n">
-        <v>149987250</v>
+        <v>18762000</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>티엑스알로보틱스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>484810</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>23450</v>
+        <v>13400</v>
       </c>
       <c r="F42" t="n">
-        <v>4264</v>
+        <v>3551</v>
       </c>
       <c r="G42" t="n">
-        <v>99990800</v>
+        <v>47583400</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>바이오비쥬</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>489460</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1824,30 +1816,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>56500</v>
+        <v>10780</v>
       </c>
       <c r="F43" t="n">
-        <v>1769</v>
+        <v>4414</v>
       </c>
       <c r="G43" t="n">
-        <v>99948500</v>
+        <v>47582920</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>와이지-원</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>019210</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1856,30 +1848,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>33600</v>
+        <v>14260</v>
       </c>
       <c r="F44" t="n">
-        <v>1488</v>
+        <v>3510</v>
       </c>
       <c r="G44" t="n">
-        <v>49996800</v>
+        <v>50052600</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>030530</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1888,94 +1880,96 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>35900</v>
+        <v>22500</v>
       </c>
       <c r="F45" t="n">
-        <v>2785</v>
+        <v>4449</v>
       </c>
       <c r="G45" t="n">
-        <v>99981500</v>
+        <v>100102500</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>032820</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 확대(숏)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9350</v>
+        <v>10630</v>
       </c>
       <c r="F46" t="n">
-        <v>10695</v>
+        <v>798</v>
       </c>
       <c r="G46" t="n">
-        <v>99998250</v>
+        <v>8482740</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>307500</v>
+        <v>17160</v>
       </c>
       <c r="F47" t="n">
-        <v>325</v>
+        <v>5549</v>
       </c>
       <c r="G47" t="n">
-        <v>99937500</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>95220840</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-4.77</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>휴메딕스</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>200670</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1984,30 +1978,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>26150</v>
+        <v>10200</v>
       </c>
       <c r="F48" t="n">
-        <v>3824</v>
+        <v>4908</v>
       </c>
       <c r="G48" t="n">
-        <v>99997600</v>
+        <v>50061600</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2016,30 +2010,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>426000</v>
+        <v>19630</v>
       </c>
       <c r="F49" t="n">
-        <v>234</v>
+        <v>2550</v>
       </c>
       <c r="G49" t="n">
-        <v>99684000</v>
+        <v>50056500</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2048,143 +2042,1505 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105200</v>
+        <v>66600</v>
       </c>
       <c r="F50" t="n">
-        <v>950</v>
+        <v>1503</v>
       </c>
       <c r="G50" t="n">
-        <v>99940000</v>
+        <v>100099800</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>54200</v>
+        <v>94200</v>
       </c>
       <c r="F51" t="n">
-        <v>2767</v>
+        <v>540</v>
       </c>
       <c r="G51" t="n">
-        <v>149971400</v>
+        <v>50868000</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>127700</v>
+        <v>34850</v>
       </c>
       <c r="F52" t="n">
-        <v>783</v>
+        <v>2812</v>
       </c>
       <c r="G52" t="n">
-        <v>99989100</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>97998200</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>425420</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>46250</v>
+        <v>60000</v>
       </c>
       <c r="F53" t="n">
-        <v>2162</v>
+        <v>1592</v>
       </c>
       <c r="G53" t="n">
-        <v>99992500</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>95520000</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.46</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>유니테스트</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>086390</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>11330</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9157</v>
+      </c>
+      <c r="G54" t="n">
+        <v>103748810</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>086450</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>21600</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2529</v>
+      </c>
+      <c r="G55" t="n">
+        <v>54626400</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F56" t="n">
+        <v>246</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5461200</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>비중 확대(숏)</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>52800</v>
+      </c>
+      <c r="F57" t="n">
+        <v>127</v>
+      </c>
+      <c r="G57" t="n">
+        <v>6705600</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>091580</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>20650</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2424</v>
+      </c>
+      <c r="G58" t="n">
+        <v>50055600</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>씨젠</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>096530</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>31900</v>
+      </c>
+      <c r="F59" t="n">
+        <v>81</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2583900</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>고영</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>098460</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>27900</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3588</v>
+      </c>
+      <c r="G60" t="n">
+        <v>100105200</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>35650</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2785</v>
+      </c>
+      <c r="G61" t="n">
+        <v>99285250</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>144960</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>8760</v>
+      </c>
+      <c r="F62" t="n">
+        <v>10695</v>
+      </c>
+      <c r="G62" t="n">
+        <v>93688200</v>
+      </c>
+      <c r="H62" t="n">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>288500</v>
+      </c>
+      <c r="F63" t="n">
+        <v>152</v>
+      </c>
+      <c r="G63" t="n">
+        <v>43852000</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>휴메딕스</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>200670</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>25850</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3824</v>
+      </c>
+      <c r="G64" t="n">
+        <v>98850400</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>386500</v>
+      </c>
+      <c r="F65" t="n">
+        <v>234</v>
+      </c>
+      <c r="G65" t="n">
+        <v>90441000</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-9.27</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>타이거일렉</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>219130</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>60400</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1657</v>
+      </c>
+      <c r="G66" t="n">
+        <v>100082800</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>226950</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>95900</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1044</v>
+      </c>
+      <c r="G67" t="n">
+        <v>100119600</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>101200</v>
+      </c>
+      <c r="F68" t="n">
+        <v>39</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3946800</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>114800</v>
+      </c>
+      <c r="F69" t="n">
+        <v>872</v>
+      </c>
+      <c r="G69" t="n">
+        <v>100105600</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F70" t="n">
+        <v>682</v>
+      </c>
+      <c r="G70" t="n">
+        <v>32736000</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>319660</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>126500</v>
+      </c>
+      <c r="F71" t="n">
+        <v>783</v>
+      </c>
+      <c r="G71" t="n">
+        <v>99049500</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>루닛</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>328130</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F72" t="n">
+        <v>11124</v>
+      </c>
+      <c r="G72" t="n">
+        <v>100116000</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>425420</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>52700</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2162</v>
+      </c>
+      <c r="G73" t="n">
+        <v>113937400</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-13.95</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>마녀공장</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>439090</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>16010</v>
+      </c>
+      <c r="F74" t="n">
+        <v>6253</v>
+      </c>
+      <c r="G74" t="n">
+        <v>100110530</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>파인엠텍</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>441270</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>9350</v>
+      </c>
+      <c r="F75" t="n">
+        <v>655</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6124250</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>475830</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>55900</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1791</v>
+      </c>
+      <c r="G76" t="n">
+        <v>100116900</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>우리기술</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>032820</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>11600</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8620</v>
+      </c>
+      <c r="G77" t="n">
+        <v>99992000</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>동성화인텍</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>033500</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>18020</v>
+      </c>
+      <c r="F78" t="n">
+        <v>5549</v>
+      </c>
+      <c r="G78" t="n">
+        <v>99992980</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>058610</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>93300</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1071</v>
+      </c>
+      <c r="G79" t="n">
+        <v>99924300</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>067310</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>35550</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2812</v>
+      </c>
+      <c r="G80" t="n">
+        <v>99966600</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>비에이치아이</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>083650</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>62800</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1592</v>
+      </c>
+      <c r="G81" t="n">
+        <v>99977600</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>유니테스트</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>086390</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>10920</v>
+      </c>
+      <c r="F82" t="n">
+        <v>9157</v>
+      </c>
+      <c r="G82" t="n">
+        <v>99994440</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>086450</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>22250</v>
+      </c>
+      <c r="F83" t="n">
+        <v>6741</v>
+      </c>
+      <c r="G83" t="n">
+        <v>149987250</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>23450</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4264</v>
+      </c>
+      <c r="G84" t="n">
+        <v>99990800</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>56500</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1769</v>
+      </c>
+      <c r="G85" t="n">
+        <v>99948500</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>씨젠</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>096530</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>33600</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1488</v>
+      </c>
+      <c r="G86" t="n">
+        <v>49996800</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>35900</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2785</v>
+      </c>
+      <c r="G87" t="n">
+        <v>99981500</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>144960</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>9350</v>
+      </c>
+      <c r="F88" t="n">
+        <v>10695</v>
+      </c>
+      <c r="G88" t="n">
+        <v>99998250</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>307500</v>
+      </c>
+      <c r="F89" t="n">
+        <v>325</v>
+      </c>
+      <c r="G89" t="n">
+        <v>99937500</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>휴메딕스</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>200670</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>26150</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3824</v>
+      </c>
+      <c r="G90" t="n">
+        <v>99997600</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>426000</v>
+      </c>
+      <c r="F91" t="n">
+        <v>234</v>
+      </c>
+      <c r="G91" t="n">
+        <v>99684000</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>105200</v>
+      </c>
+      <c r="F92" t="n">
+        <v>950</v>
+      </c>
+      <c r="G92" t="n">
+        <v>99940000</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2767</v>
+      </c>
+      <c r="G93" t="n">
+        <v>149971400</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>319660</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>127700</v>
+      </c>
+      <c r="F94" t="n">
+        <v>783</v>
+      </c>
+      <c r="G94" t="n">
+        <v>99989100</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>425420</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>46250</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2162</v>
+      </c>
+      <c r="G95" t="n">
+        <v>99992500</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>파인엠텍</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>441270</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E96" t="n">
         <v>8320</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F96" t="n">
         <v>6009</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G96" t="n">
         <v>49994880</v>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,27 +806,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>68900</v>
+        <v>21200</v>
       </c>
       <c r="F12" t="n">
-        <v>260</v>
+        <v>2245</v>
       </c>
       <c r="G12" t="n">
-        <v>17914000</v>
+        <v>47594000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -838,31 +838,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>91300</v>
+        <v>68900</v>
       </c>
       <c r="F13" t="n">
-        <v>531</v>
+        <v>260</v>
       </c>
       <c r="G13" t="n">
-        <v>48480300</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.14</v>
-      </c>
+        <v>17914000</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -882,19 +880,21 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>91300</v>
       </c>
       <c r="F14" t="n">
-        <v>208</v>
+        <v>531</v>
       </c>
       <c r="G14" t="n">
-        <v>18990400</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>48480300</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.14</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -904,27 +904,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>19930</v>
+        <v>91300</v>
       </c>
       <c r="F15" t="n">
-        <v>7360</v>
+        <v>208</v>
       </c>
       <c r="G15" t="n">
-        <v>146684800</v>
+        <v>18990400</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>22500</v>
+        <v>19930</v>
       </c>
       <c r="F16" t="n">
-        <v>1972</v>
+        <v>7360</v>
       </c>
       <c r="G16" t="n">
-        <v>44370000</v>
+        <v>146684800</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>51100</v>
+        <v>22500</v>
       </c>
       <c r="F17" t="n">
-        <v>592</v>
+        <v>1972</v>
       </c>
       <c r="G17" t="n">
-        <v>30251200</v>
+        <v>44370000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>20550</v>
+        <v>51100</v>
       </c>
       <c r="F18" t="n">
-        <v>108</v>
+        <v>592</v>
       </c>
       <c r="G18" t="n">
-        <v>2219400</v>
+        <v>30251200</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1032,27 +1032,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>케이아이엔엑스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>093320</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>139000</v>
+        <v>20550</v>
       </c>
       <c r="F19" t="n">
-        <v>411</v>
+        <v>108</v>
       </c>
       <c r="G19" t="n">
-        <v>57129000</v>
+        <v>2219400</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>케이아이엔엑스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>093320</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>31450</v>
+        <v>139000</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>411</v>
       </c>
       <c r="G20" t="n">
-        <v>1761200</v>
+        <v>57129000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>27150</v>
+        <v>31450</v>
       </c>
       <c r="F21" t="n">
-        <v>784</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>21285600</v>
+        <v>1761200</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1128,27 +1128,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>098460</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>41300</v>
+        <v>27150</v>
       </c>
       <c r="F22" t="n">
-        <v>1152</v>
+        <v>784</v>
       </c>
       <c r="G22" t="n">
-        <v>47577600</v>
+        <v>21285600</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>284000</v>
+        <v>41300</v>
       </c>
       <c r="F23" t="n">
-        <v>235</v>
+        <v>1152</v>
       </c>
       <c r="G23" t="n">
-        <v>66740000</v>
+        <v>47577600</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>21100</v>
+        <v>284000</v>
       </c>
       <c r="F24" t="n">
-        <v>902</v>
+        <v>235</v>
       </c>
       <c r="G24" t="n">
-        <v>19032200</v>
+        <v>66740000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1224,27 +1224,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>큐브엔터</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>182360</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6110</v>
+        <v>21100</v>
       </c>
       <c r="F25" t="n">
-        <v>4673</v>
+        <v>902</v>
       </c>
       <c r="G25" t="n">
-        <v>28552030</v>
+        <v>19032200</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1256,27 +1256,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>큐브엔터</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>182360</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>277000</v>
+        <v>6110</v>
       </c>
       <c r="F26" t="n">
-        <v>102</v>
+        <v>4673</v>
       </c>
       <c r="G26" t="n">
-        <v>28254000</v>
+        <v>28552030</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,27 +1288,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>369000</v>
+        <v>277000</v>
       </c>
       <c r="F27" t="n">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="G27" t="n">
-        <v>47601000</v>
+        <v>28254000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,27 +1320,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>62300</v>
+        <v>369000</v>
       </c>
       <c r="F28" t="n">
-        <v>435</v>
+        <v>129</v>
       </c>
       <c r="G28" t="n">
-        <v>27100500</v>
+        <v>47601000</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>226950</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>99100</v>
+        <v>62300</v>
       </c>
       <c r="F29" t="n">
-        <v>372</v>
+        <v>435</v>
       </c>
       <c r="G29" t="n">
-        <v>36865200</v>
+        <v>27100500</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>226950</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>91900</v>
+        <v>99100</v>
       </c>
       <c r="F30" t="n">
-        <v>471</v>
+        <v>372</v>
       </c>
       <c r="G30" t="n">
-        <v>43284900</v>
+        <v>36865200</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1430,13 +1430,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>115800</v>
+        <v>91900</v>
       </c>
       <c r="F31" t="n">
-        <v>379</v>
+        <v>471</v>
       </c>
       <c r="G31" t="n">
-        <v>43888200</v>
+        <v>43284900</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>46250</v>
+        <v>115800</v>
       </c>
       <c r="F32" t="n">
-        <v>1673</v>
+        <v>379</v>
       </c>
       <c r="G32" t="n">
-        <v>77376250</v>
+        <v>43888200</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,27 +1480,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2710</v>
+        <v>46250</v>
       </c>
       <c r="F33" t="n">
-        <v>14048</v>
+        <v>1673</v>
       </c>
       <c r="G33" t="n">
-        <v>38070080</v>
+        <v>77376250</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,27 +1512,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>290720</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>34500</v>
+        <v>2710</v>
       </c>
       <c r="F34" t="n">
-        <v>828</v>
+        <v>14048</v>
       </c>
       <c r="G34" t="n">
-        <v>28566000</v>
+        <v>38070080</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,27 +1544,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>8700</v>
+        <v>34500</v>
       </c>
       <c r="F35" t="n">
-        <v>2372</v>
+        <v>828</v>
       </c>
       <c r="G35" t="n">
-        <v>20636400</v>
+        <v>28566000</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,27 +1576,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>워트</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>396470</t>
+          <t>328130</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6630</v>
+        <v>8700</v>
       </c>
       <c r="F36" t="n">
-        <v>7178</v>
+        <v>2372</v>
       </c>
       <c r="G36" t="n">
-        <v>47590140</v>
+        <v>20636400</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,27 +1608,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>마녀공장</t>
+          <t>워트</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>439090</t>
+          <t>396470</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>15890</v>
+        <v>6630</v>
       </c>
       <c r="F37" t="n">
-        <v>2659</v>
+        <v>7178</v>
       </c>
       <c r="G37" t="n">
-        <v>42251510</v>
+        <v>47590140</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,31 +1640,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>마녀공장</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>439090</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>8070</v>
+        <v>15890</v>
       </c>
       <c r="F38" t="n">
-        <v>5354</v>
+        <v>2659</v>
       </c>
       <c r="G38" t="n">
-        <v>43206780</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-3</v>
-      </c>
+        <v>42251510</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1674,29 +1672,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>엔젤로보틱스</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>455900</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>21300</v>
+        <v>8070</v>
       </c>
       <c r="F39" t="n">
-        <v>1787</v>
+        <v>5354</v>
       </c>
       <c r="G39" t="n">
-        <v>38063100</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>43206780</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>에스오에스랩</t>
+          <t>엔젤로보틱스</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>464080</t>
+          <t>455900</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>9980</v>
+        <v>21300</v>
       </c>
       <c r="F40" t="n">
-        <v>4768</v>
+        <v>1787</v>
       </c>
       <c r="G40" t="n">
-        <v>47584640</v>
+        <v>38063100</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1738,27 +1738,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>에스오에스랩</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>475830</t>
+          <t>464080</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53000</v>
+        <v>9980</v>
       </c>
       <c r="F41" t="n">
-        <v>354</v>
+        <v>4768</v>
       </c>
       <c r="G41" t="n">
-        <v>18762000</v>
+        <v>47584640</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1770,27 +1770,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>티엑스알로보틱스</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>484810</t>
+          <t>475830</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13400</v>
+        <v>53000</v>
       </c>
       <c r="F42" t="n">
-        <v>3551</v>
+        <v>354</v>
       </c>
       <c r="G42" t="n">
-        <v>47583400</v>
+        <v>18762000</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>바이오비쥬</t>
+          <t>티엑스알로보틱스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>489460</t>
+          <t>484810</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1816,45 +1816,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10780</v>
+        <v>13400</v>
       </c>
       <c r="F43" t="n">
-        <v>4414</v>
+        <v>3551</v>
       </c>
       <c r="G43" t="n">
-        <v>47582920</v>
+        <v>47583400</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>와이지-원</t>
+          <t>바이오비쥬</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>019210</t>
+          <t>489460</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>14260</v>
+        <v>10780</v>
       </c>
       <c r="F44" t="n">
-        <v>3510</v>
+        <v>4414</v>
       </c>
       <c r="G44" t="n">
-        <v>50052600</v>
+        <v>47582920</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1866,27 +1866,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>와이지-원</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>019210</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>22500</v>
+        <v>14260</v>
       </c>
       <c r="F45" t="n">
-        <v>4449</v>
+        <v>3510</v>
       </c>
       <c r="G45" t="n">
-        <v>100102500</v>
+        <v>50052600</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1898,27 +1898,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>030530</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대(숏)</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>10630</v>
+        <v>22500</v>
       </c>
       <c r="F46" t="n">
-        <v>798</v>
+        <v>4449</v>
       </c>
       <c r="G46" t="n">
-        <v>8482740</v>
+        <v>100102500</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1930,31 +1930,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>032820</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대(숏)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17160</v>
+        <v>10630</v>
       </c>
       <c r="F47" t="n">
-        <v>5549</v>
+        <v>798</v>
       </c>
       <c r="G47" t="n">
-        <v>95220840</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-4.77</v>
-      </c>
+        <v>8482740</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1964,29 +1962,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>10200</v>
+        <v>17160</v>
       </c>
       <c r="F48" t="n">
-        <v>4908</v>
+        <v>5549</v>
       </c>
       <c r="G48" t="n">
-        <v>50061600</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>95220840</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-4.77</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1996,27 +1996,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>19630</v>
+        <v>10200</v>
       </c>
       <c r="F49" t="n">
-        <v>2550</v>
+        <v>4908</v>
       </c>
       <c r="G49" t="n">
-        <v>50056500</v>
+        <v>50061600</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>66600</v>
+        <v>19630</v>
       </c>
       <c r="F50" t="n">
-        <v>1503</v>
+        <v>2550</v>
       </c>
       <c r="G50" t="n">
-        <v>100099800</v>
+        <v>50056500</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2060,27 +2060,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>94200</v>
+        <v>66600</v>
       </c>
       <c r="F51" t="n">
-        <v>540</v>
+        <v>1503</v>
       </c>
       <c r="G51" t="n">
-        <v>50868000</v>
+        <v>100099800</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2092,31 +2092,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>34850</v>
+        <v>94200</v>
       </c>
       <c r="F52" t="n">
-        <v>2812</v>
+        <v>540</v>
       </c>
       <c r="G52" t="n">
-        <v>97998200</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1.97</v>
-      </c>
+        <v>50868000</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2126,12 +2124,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2140,16 +2138,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>60000</v>
+        <v>34850</v>
       </c>
       <c r="F53" t="n">
-        <v>1592</v>
+        <v>2812</v>
       </c>
       <c r="G53" t="n">
-        <v>95520000</v>
+        <v>97998200</v>
       </c>
       <c r="H53" t="n">
-        <v>4.46</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="54">
@@ -2160,12 +2158,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2174,16 +2172,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>11330</v>
+        <v>60000</v>
       </c>
       <c r="F54" t="n">
-        <v>9157</v>
+        <v>1592</v>
       </c>
       <c r="G54" t="n">
-        <v>103748810</v>
+        <v>95520000</v>
       </c>
       <c r="H54" t="n">
-        <v>3.75</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="55">
@@ -2194,29 +2192,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>21600</v>
+        <v>11330</v>
       </c>
       <c r="F55" t="n">
-        <v>2529</v>
+        <v>9157</v>
       </c>
       <c r="G55" t="n">
-        <v>54626400</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>103748810</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3.75</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>22200</v>
+        <v>21600</v>
       </c>
       <c r="F56" t="n">
-        <v>246</v>
+        <v>2529</v>
       </c>
       <c r="G56" t="n">
-        <v>5461200</v>
+        <v>54626400</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2258,27 +2258,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대(숏)</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>52800</v>
+        <v>22200</v>
       </c>
       <c r="F57" t="n">
-        <v>127</v>
+        <v>246</v>
       </c>
       <c r="G57" t="n">
-        <v>6705600</v>
+        <v>5461200</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2290,27 +2290,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대(숏)</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>20650</v>
+        <v>52800</v>
       </c>
       <c r="F58" t="n">
-        <v>2424</v>
+        <v>127</v>
       </c>
       <c r="G58" t="n">
-        <v>50055600</v>
+        <v>6705600</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2322,27 +2322,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>31900</v>
+        <v>20650</v>
       </c>
       <c r="F59" t="n">
-        <v>81</v>
+        <v>2424</v>
       </c>
       <c r="G59" t="n">
-        <v>2583900</v>
+        <v>50055600</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2354,27 +2354,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>27900</v>
+        <v>31900</v>
       </c>
       <c r="F60" t="n">
-        <v>3588</v>
+        <v>81</v>
       </c>
       <c r="G60" t="n">
-        <v>100105200</v>
+        <v>2583900</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2386,31 +2386,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>098460</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>35650</v>
+        <v>27900</v>
       </c>
       <c r="F61" t="n">
-        <v>2785</v>
+        <v>3588</v>
       </c>
       <c r="G61" t="n">
-        <v>99285250</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.7</v>
-      </c>
+        <v>100105200</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2420,12 +2418,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2434,16 +2432,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>8760</v>
+        <v>35650</v>
       </c>
       <c r="F62" t="n">
-        <v>10695</v>
+        <v>2785</v>
       </c>
       <c r="G62" t="n">
-        <v>93688200</v>
+        <v>99285250</v>
       </c>
       <c r="H62" t="n">
-        <v>6.31</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="63">
@@ -2454,29 +2452,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>288500</v>
+        <v>8760</v>
       </c>
       <c r="F63" t="n">
-        <v>152</v>
+        <v>10695</v>
       </c>
       <c r="G63" t="n">
-        <v>43852000</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>93688200</v>
+      </c>
+      <c r="H63" t="n">
+        <v>6.31</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2486,31 +2486,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>휴메딕스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>200670</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>25850</v>
+        <v>288500</v>
       </c>
       <c r="F64" t="n">
-        <v>3824</v>
+        <v>152</v>
       </c>
       <c r="G64" t="n">
-        <v>98850400</v>
-      </c>
-      <c r="H64" t="n">
-        <v>1.15</v>
-      </c>
+        <v>43852000</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2520,12 +2518,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>휴메딕스</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>200670</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2534,16 +2532,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>386500</v>
+        <v>25850</v>
       </c>
       <c r="F65" t="n">
-        <v>234</v>
+        <v>3824</v>
       </c>
       <c r="G65" t="n">
-        <v>90441000</v>
+        <v>98850400</v>
       </c>
       <c r="H65" t="n">
-        <v>-9.27</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="66">
@@ -2554,29 +2552,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>60400</v>
+        <v>386500</v>
       </c>
       <c r="F66" t="n">
-        <v>1657</v>
+        <v>234</v>
       </c>
       <c r="G66" t="n">
-        <v>100082800</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>90441000</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-9.27</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>226950</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2600,13 +2600,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>95900</v>
+        <v>60400</v>
       </c>
       <c r="F67" t="n">
-        <v>1044</v>
+        <v>1657</v>
       </c>
       <c r="G67" t="n">
-        <v>100119600</v>
+        <v>100082800</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2618,27 +2618,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>226950</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>101200</v>
+        <v>95900</v>
       </c>
       <c r="F68" t="n">
-        <v>39</v>
+        <v>1044</v>
       </c>
       <c r="G68" t="n">
-        <v>3946800</v>
+        <v>100119600</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2650,27 +2650,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>114800</v>
+        <v>101200</v>
       </c>
       <c r="F69" t="n">
-        <v>872</v>
+        <v>39</v>
       </c>
       <c r="G69" t="n">
-        <v>100105600</v>
+        <v>3946800</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2682,27 +2682,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>48000</v>
+        <v>114800</v>
       </c>
       <c r="F70" t="n">
-        <v>682</v>
+        <v>872</v>
       </c>
       <c r="G70" t="n">
-        <v>32736000</v>
+        <v>100105600</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2714,31 +2714,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>126500</v>
+        <v>48000</v>
       </c>
       <c r="F71" t="n">
-        <v>783</v>
+        <v>682</v>
       </c>
       <c r="G71" t="n">
-        <v>99049500</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+        <v>32736000</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2748,29 +2746,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>9000</v>
+        <v>126500</v>
       </c>
       <c r="F72" t="n">
-        <v>11124</v>
+        <v>783</v>
       </c>
       <c r="G72" t="n">
-        <v>100116000</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>99049500</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.9399999999999999</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2780,31 +2780,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>425420</t>
+          <t>328130</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>52700</v>
+        <v>9000</v>
       </c>
       <c r="F73" t="n">
-        <v>2162</v>
+        <v>11124</v>
       </c>
       <c r="G73" t="n">
-        <v>113937400</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-13.95</v>
-      </c>
+        <v>100116000</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2814,29 +2812,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>마녀공장</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>439090</t>
+          <t>425420</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>16010</v>
+        <v>52700</v>
       </c>
       <c r="F74" t="n">
-        <v>6253</v>
+        <v>2162</v>
       </c>
       <c r="G74" t="n">
-        <v>100110530</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
+        <v>113937400</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-13.95</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2846,27 +2846,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>마녀공장</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>439090</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>9350</v>
+        <v>16010</v>
       </c>
       <c r="F75" t="n">
-        <v>655</v>
+        <v>6253</v>
       </c>
       <c r="G75" t="n">
-        <v>6124250</v>
+        <v>100110530</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2878,44 +2878,44 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>475830</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>55900</v>
+        <v>9350</v>
       </c>
       <c r="F76" t="n">
-        <v>1791</v>
+        <v>655</v>
       </c>
       <c r="G76" t="n">
-        <v>100116900</v>
+        <v>6124250</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>475830</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2924,13 +2924,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>11600</v>
+        <v>55900</v>
       </c>
       <c r="F77" t="n">
-        <v>8620</v>
+        <v>1791</v>
       </c>
       <c r="G77" t="n">
-        <v>99992000</v>
+        <v>100116900</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2942,27 +2942,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>032820</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>18020</v>
+        <v>11600</v>
       </c>
       <c r="F78" t="n">
-        <v>5549</v>
+        <v>8620</v>
       </c>
       <c r="G78" t="n">
-        <v>99992980</v>
+        <v>99992000</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2974,27 +2974,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>93300</v>
+        <v>18020</v>
       </c>
       <c r="F79" t="n">
-        <v>1071</v>
+        <v>5549</v>
       </c>
       <c r="G79" t="n">
-        <v>99924300</v>
+        <v>99992980</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3020,13 +3020,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>35550</v>
+        <v>93300</v>
       </c>
       <c r="F80" t="n">
-        <v>2812</v>
+        <v>1071</v>
       </c>
       <c r="G80" t="n">
-        <v>99966600</v>
+        <v>99924300</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3052,13 +3052,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>62800</v>
+        <v>35550</v>
       </c>
       <c r="F81" t="n">
-        <v>1592</v>
+        <v>2812</v>
       </c>
       <c r="G81" t="n">
-        <v>99977600</v>
+        <v>99966600</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3070,27 +3070,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>10920</v>
+        <v>62800</v>
       </c>
       <c r="F82" t="n">
-        <v>9157</v>
+        <v>1592</v>
       </c>
       <c r="G82" t="n">
-        <v>99994440</v>
+        <v>99977600</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>22250</v>
+        <v>10920</v>
       </c>
       <c r="F83" t="n">
-        <v>6741</v>
+        <v>9157</v>
       </c>
       <c r="G83" t="n">
-        <v>149987250</v>
+        <v>99994440</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>23450</v>
+        <v>22250</v>
       </c>
       <c r="F84" t="n">
-        <v>4264</v>
+        <v>6741</v>
       </c>
       <c r="G84" t="n">
-        <v>99990800</v>
+        <v>149987250</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3166,27 +3166,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>56500</v>
+        <v>23450</v>
       </c>
       <c r="F85" t="n">
-        <v>1769</v>
+        <v>4264</v>
       </c>
       <c r="G85" t="n">
-        <v>99948500</v>
+        <v>99990800</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3198,27 +3198,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>33600</v>
+        <v>56500</v>
       </c>
       <c r="F86" t="n">
-        <v>1488</v>
+        <v>1769</v>
       </c>
       <c r="G86" t="n">
-        <v>49996800</v>
+        <v>99948500</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3230,27 +3230,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>35900</v>
+        <v>33600</v>
       </c>
       <c r="F87" t="n">
-        <v>2785</v>
+        <v>1488</v>
       </c>
       <c r="G87" t="n">
-        <v>99981500</v>
+        <v>49996800</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3276,13 +3276,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>9350</v>
+        <v>35900</v>
       </c>
       <c r="F88" t="n">
-        <v>10695</v>
+        <v>2785</v>
       </c>
       <c r="G88" t="n">
-        <v>99998250</v>
+        <v>99981500</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3294,27 +3294,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>307500</v>
+        <v>9350</v>
       </c>
       <c r="F89" t="n">
-        <v>325</v>
+        <v>10695</v>
       </c>
       <c r="G89" t="n">
-        <v>99937500</v>
+        <v>99998250</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3326,27 +3326,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>휴메딕스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>200670</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>26150</v>
+        <v>307500</v>
       </c>
       <c r="F90" t="n">
-        <v>3824</v>
+        <v>325</v>
       </c>
       <c r="G90" t="n">
-        <v>99997600</v>
+        <v>99937500</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3358,27 +3358,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>휴메딕스</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>200670</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>426000</v>
+        <v>26150</v>
       </c>
       <c r="F91" t="n">
-        <v>234</v>
+        <v>3824</v>
       </c>
       <c r="G91" t="n">
-        <v>99684000</v>
+        <v>99997600</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3390,12 +3390,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3404,13 +3404,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>105200</v>
+        <v>426000</v>
       </c>
       <c r="F92" t="n">
-        <v>950</v>
+        <v>234</v>
       </c>
       <c r="G92" t="n">
-        <v>99940000</v>
+        <v>99684000</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3422,12 +3422,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>54200</v>
+        <v>105200</v>
       </c>
       <c r="F93" t="n">
-        <v>2767</v>
+        <v>950</v>
       </c>
       <c r="G93" t="n">
-        <v>149971400</v>
+        <v>99940000</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3454,27 +3454,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>127700</v>
+        <v>54200</v>
       </c>
       <c r="F94" t="n">
-        <v>783</v>
+        <v>2767</v>
       </c>
       <c r="G94" t="n">
-        <v>99989100</v>
+        <v>149971400</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3486,12 +3486,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>425420</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3500,13 +3500,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>46250</v>
+        <v>127700</v>
       </c>
       <c r="F95" t="n">
-        <v>2162</v>
+        <v>783</v>
       </c>
       <c r="G95" t="n">
-        <v>99992500</v>
+        <v>99989100</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3518,29 +3518,61 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>425420</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>편입(숏)</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>46250</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2162</v>
+      </c>
+      <c r="G96" t="n">
+        <v>99992500</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>파인엠텍</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>441270</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>8320</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>6009</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G97" t="n">
         <v>49994880</v>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,21 +782,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>21200</v>
       </c>
       <c r="F11" t="n">
-        <v>2550</v>
+        <v>305</v>
       </c>
       <c r="G11" t="n">
-        <v>54060000</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
+        <v>6466000</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -806,27 +804,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>21200</v>
+        <v>68900</v>
       </c>
       <c r="F12" t="n">
-        <v>2245</v>
+        <v>260</v>
       </c>
       <c r="G12" t="n">
-        <v>47594000</v>
+        <v>17914000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -838,29 +836,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>68900</v>
+        <v>91300</v>
       </c>
       <c r="F13" t="n">
-        <v>260</v>
+        <v>531</v>
       </c>
       <c r="G13" t="n">
-        <v>17914000</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>48480300</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -880,21 +880,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>91300</v>
       </c>
       <c r="F14" t="n">
-        <v>531</v>
+        <v>208</v>
       </c>
       <c r="G14" t="n">
-        <v>48480300</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.14</v>
-      </c>
+        <v>18990400</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -904,27 +902,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>91300</v>
+        <v>19930</v>
       </c>
       <c r="F15" t="n">
-        <v>208</v>
+        <v>7360</v>
       </c>
       <c r="G15" t="n">
-        <v>18990400</v>
+        <v>146684800</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -936,12 +934,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -950,13 +948,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19930</v>
+        <v>22500</v>
       </c>
       <c r="F16" t="n">
-        <v>7360</v>
+        <v>1972</v>
       </c>
       <c r="G16" t="n">
-        <v>146684800</v>
+        <v>44370000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -968,12 +966,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -982,13 +980,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>22500</v>
+        <v>51100</v>
       </c>
       <c r="F17" t="n">
-        <v>1972</v>
+        <v>592</v>
       </c>
       <c r="G17" t="n">
-        <v>44370000</v>
+        <v>30251200</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1000,12 +998,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1014,13 +1012,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>51100</v>
+        <v>20550</v>
       </c>
       <c r="F18" t="n">
-        <v>592</v>
+        <v>108</v>
       </c>
       <c r="G18" t="n">
-        <v>30251200</v>
+        <v>2219400</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1032,27 +1030,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>케이아이엔엑스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>093320</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>20550</v>
+        <v>139000</v>
       </c>
       <c r="F19" t="n">
-        <v>108</v>
+        <v>411</v>
       </c>
       <c r="G19" t="n">
-        <v>2219400</v>
+        <v>57129000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1064,27 +1062,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>케이아이엔엑스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>093320</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>139000</v>
+        <v>31450</v>
       </c>
       <c r="F20" t="n">
-        <v>411</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>57129000</v>
+        <v>1761200</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1096,12 +1094,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>098460</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1110,13 +1108,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>31450</v>
+        <v>27150</v>
       </c>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>784</v>
       </c>
       <c r="G21" t="n">
-        <v>1761200</v>
+        <v>21285600</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1128,27 +1126,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>27150</v>
+        <v>41300</v>
       </c>
       <c r="F22" t="n">
-        <v>784</v>
+        <v>1152</v>
       </c>
       <c r="G22" t="n">
-        <v>21285600</v>
+        <v>47577600</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1160,12 +1158,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1174,13 +1172,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>41300</v>
+        <v>284000</v>
       </c>
       <c r="F23" t="n">
-        <v>1152</v>
+        <v>235</v>
       </c>
       <c r="G23" t="n">
-        <v>47577600</v>
+        <v>66740000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1192,12 +1190,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1206,13 +1204,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>284000</v>
+        <v>21100</v>
       </c>
       <c r="F24" t="n">
-        <v>235</v>
+        <v>902</v>
       </c>
       <c r="G24" t="n">
-        <v>66740000</v>
+        <v>19032200</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1224,27 +1222,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>큐브엔터</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>182360</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>21100</v>
+        <v>6110</v>
       </c>
       <c r="F25" t="n">
-        <v>902</v>
+        <v>4673</v>
       </c>
       <c r="G25" t="n">
-        <v>19032200</v>
+        <v>28552030</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1256,27 +1254,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>큐브엔터</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>182360</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6110</v>
+        <v>277000</v>
       </c>
       <c r="F26" t="n">
-        <v>4673</v>
+        <v>102</v>
       </c>
       <c r="G26" t="n">
-        <v>28552030</v>
+        <v>28254000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,27 +1286,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>277000</v>
+        <v>369000</v>
       </c>
       <c r="F27" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="G27" t="n">
-        <v>28254000</v>
+        <v>47601000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,27 +1318,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>369000</v>
+        <v>62300</v>
       </c>
       <c r="F28" t="n">
-        <v>129</v>
+        <v>435</v>
       </c>
       <c r="G28" t="n">
-        <v>47601000</v>
+        <v>27100500</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,12 +1350,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>226950</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1366,13 +1364,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>62300</v>
+        <v>99100</v>
       </c>
       <c r="F29" t="n">
-        <v>435</v>
+        <v>372</v>
       </c>
       <c r="G29" t="n">
-        <v>27100500</v>
+        <v>36865200</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,12 +1382,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>226950</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1398,13 +1396,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>99100</v>
+        <v>91900</v>
       </c>
       <c r="F30" t="n">
-        <v>372</v>
+        <v>471</v>
       </c>
       <c r="G30" t="n">
-        <v>36865200</v>
+        <v>43284900</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,12 +1414,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1430,13 +1428,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>91900</v>
+        <v>115800</v>
       </c>
       <c r="F31" t="n">
-        <v>471</v>
+        <v>379</v>
       </c>
       <c r="G31" t="n">
-        <v>43284900</v>
+        <v>43888200</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1462,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>115800</v>
+        <v>46250</v>
       </c>
       <c r="F32" t="n">
-        <v>379</v>
+        <v>1673</v>
       </c>
       <c r="G32" t="n">
-        <v>43888200</v>
+        <v>77376250</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,27 +1478,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>290720</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>46250</v>
+        <v>2710</v>
       </c>
       <c r="F33" t="n">
-        <v>1673</v>
+        <v>14048</v>
       </c>
       <c r="G33" t="n">
-        <v>77376250</v>
+        <v>38070080</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,27 +1510,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2710</v>
+        <v>34500</v>
       </c>
       <c r="F34" t="n">
-        <v>14048</v>
+        <v>828</v>
       </c>
       <c r="G34" t="n">
-        <v>38070080</v>
+        <v>28566000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,27 +1542,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>328130</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>34500</v>
+        <v>8700</v>
       </c>
       <c r="F35" t="n">
-        <v>828</v>
+        <v>2372</v>
       </c>
       <c r="G35" t="n">
-        <v>28566000</v>
+        <v>20636400</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,27 +1574,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>워트</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>396470</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>8700</v>
+        <v>6630</v>
       </c>
       <c r="F36" t="n">
-        <v>2372</v>
+        <v>7178</v>
       </c>
       <c r="G36" t="n">
-        <v>20636400</v>
+        <v>47590140</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,27 +1606,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>워트</t>
+          <t>마녀공장</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>396470</t>
+          <t>439090</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6630</v>
+        <v>15890</v>
       </c>
       <c r="F37" t="n">
-        <v>7178</v>
+        <v>2659</v>
       </c>
       <c r="G37" t="n">
-        <v>47590140</v>
+        <v>42251510</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,29 +1638,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>마녀공장</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>439090</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15890</v>
+        <v>8070</v>
       </c>
       <c r="F38" t="n">
-        <v>2659</v>
+        <v>5354</v>
       </c>
       <c r="G38" t="n">
-        <v>42251510</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>43206780</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1672,31 +1672,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>엔젤로보틱스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>455900</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>8070</v>
+        <v>21300</v>
       </c>
       <c r="F39" t="n">
-        <v>5354</v>
+        <v>1787</v>
       </c>
       <c r="G39" t="n">
-        <v>43206780</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-3</v>
-      </c>
+        <v>38063100</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1706,12 +1704,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>엔젤로보틱스</t>
+          <t>에스오에스랩</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>455900</t>
+          <t>464080</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1720,13 +1718,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>21300</v>
+        <v>9980</v>
       </c>
       <c r="F40" t="n">
-        <v>1787</v>
+        <v>4768</v>
       </c>
       <c r="G40" t="n">
-        <v>38063100</v>
+        <v>47584640</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1738,27 +1736,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>에스오에스랩</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>464080</t>
+          <t>475830</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>9980</v>
+        <v>53000</v>
       </c>
       <c r="F41" t="n">
-        <v>4768</v>
+        <v>354</v>
       </c>
       <c r="G41" t="n">
-        <v>47584640</v>
+        <v>18762000</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1770,27 +1768,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>티엑스알로보틱스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>475830</t>
+          <t>484810</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53000</v>
+        <v>13400</v>
       </c>
       <c r="F42" t="n">
-        <v>354</v>
+        <v>3551</v>
       </c>
       <c r="G42" t="n">
-        <v>18762000</v>
+        <v>47583400</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1802,12 +1800,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>티엑스알로보틱스</t>
+          <t>바이오비쥬</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>484810</t>
+          <t>489460</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1816,45 +1814,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>13400</v>
+        <v>10780</v>
       </c>
       <c r="F43" t="n">
-        <v>3551</v>
+        <v>4414</v>
       </c>
       <c r="G43" t="n">
-        <v>47583400</v>
+        <v>47582920</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>바이오비쥬</t>
+          <t>와이지-원</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>489460</t>
+          <t>019210</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10780</v>
+        <v>14260</v>
       </c>
       <c r="F44" t="n">
-        <v>4414</v>
+        <v>3510</v>
       </c>
       <c r="G44" t="n">
-        <v>47582920</v>
+        <v>50052600</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1866,27 +1864,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>와이지-원</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>019210</t>
+          <t>030530</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>14260</v>
+        <v>22500</v>
       </c>
       <c r="F45" t="n">
-        <v>3510</v>
+        <v>4449</v>
       </c>
       <c r="G45" t="n">
-        <v>50052600</v>
+        <v>100102500</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1898,27 +1896,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>032820</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 확대(숏)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>22500</v>
+        <v>10630</v>
       </c>
       <c r="F46" t="n">
-        <v>4449</v>
+        <v>798</v>
       </c>
       <c r="G46" t="n">
-        <v>100102500</v>
+        <v>8482740</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1930,29 +1928,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 확대(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>10630</v>
+        <v>17160</v>
       </c>
       <c r="F47" t="n">
-        <v>798</v>
+        <v>5549</v>
       </c>
       <c r="G47" t="n">
-        <v>8482740</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>95220840</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-4.77</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1962,31 +1962,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>17160</v>
+        <v>10200</v>
       </c>
       <c r="F48" t="n">
-        <v>5549</v>
+        <v>4908</v>
       </c>
       <c r="G48" t="n">
-        <v>95220840</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-4.77</v>
-      </c>
+        <v>50061600</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1996,27 +1994,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10200</v>
+        <v>19630</v>
       </c>
       <c r="F49" t="n">
-        <v>4908</v>
+        <v>2550</v>
       </c>
       <c r="G49" t="n">
-        <v>50061600</v>
+        <v>50056500</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2028,12 +2026,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2042,13 +2040,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>19630</v>
+        <v>66600</v>
       </c>
       <c r="F50" t="n">
-        <v>2550</v>
+        <v>1503</v>
       </c>
       <c r="G50" t="n">
-        <v>50056500</v>
+        <v>100099800</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2060,27 +2058,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>66600</v>
+        <v>94200</v>
       </c>
       <c r="F51" t="n">
-        <v>1503</v>
+        <v>540</v>
       </c>
       <c r="G51" t="n">
-        <v>100099800</v>
+        <v>50868000</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2092,29 +2090,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>94200</v>
+        <v>34850</v>
       </c>
       <c r="F52" t="n">
-        <v>540</v>
+        <v>2812</v>
       </c>
       <c r="G52" t="n">
-        <v>50868000</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>97998200</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2138,16 +2138,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>34850</v>
+        <v>60000</v>
       </c>
       <c r="F53" t="n">
-        <v>2812</v>
+        <v>1592</v>
       </c>
       <c r="G53" t="n">
-        <v>97998200</v>
+        <v>95520000</v>
       </c>
       <c r="H53" t="n">
-        <v>1.97</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="54">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>60000</v>
+        <v>11330</v>
       </c>
       <c r="F54" t="n">
-        <v>1592</v>
+        <v>9157</v>
       </c>
       <c r="G54" t="n">
-        <v>95520000</v>
+        <v>103748810</v>
       </c>
       <c r="H54" t="n">
-        <v>4.46</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="55">
@@ -2192,31 +2192,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>11330</v>
+        <v>21600</v>
       </c>
       <c r="F55" t="n">
-        <v>9157</v>
+        <v>2529</v>
       </c>
       <c r="G55" t="n">
-        <v>103748810</v>
-      </c>
-      <c r="H55" t="n">
-        <v>3.75</v>
-      </c>
+        <v>54626400</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2226,12 +2224,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2240,13 +2238,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>21600</v>
+        <v>22200</v>
       </c>
       <c r="F56" t="n">
-        <v>2529</v>
+        <v>246</v>
       </c>
       <c r="G56" t="n">
-        <v>54626400</v>
+        <v>5461200</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2258,27 +2256,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 확대(숏)</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>22200</v>
+        <v>52800</v>
       </c>
       <c r="F57" t="n">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="G57" t="n">
-        <v>5461200</v>
+        <v>6705600</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2290,27 +2288,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 확대(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>52800</v>
+        <v>20650</v>
       </c>
       <c r="F58" t="n">
-        <v>127</v>
+        <v>2424</v>
       </c>
       <c r="G58" t="n">
-        <v>6705600</v>
+        <v>50055600</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2322,27 +2320,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>20650</v>
+        <v>31900</v>
       </c>
       <c r="F59" t="n">
-        <v>2424</v>
+        <v>81</v>
       </c>
       <c r="G59" t="n">
-        <v>50055600</v>
+        <v>2583900</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2354,27 +2352,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>098460</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>31900</v>
+        <v>27900</v>
       </c>
       <c r="F60" t="n">
-        <v>81</v>
+        <v>3588</v>
       </c>
       <c r="G60" t="n">
-        <v>2583900</v>
+        <v>100105200</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2386,29 +2384,31 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>27900</v>
+        <v>35650</v>
       </c>
       <c r="F61" t="n">
-        <v>3588</v>
+        <v>2785</v>
       </c>
       <c r="G61" t="n">
-        <v>100105200</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>99285250</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2432,16 +2432,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>35650</v>
+        <v>8760</v>
       </c>
       <c r="F62" t="n">
-        <v>2785</v>
+        <v>10695</v>
       </c>
       <c r="G62" t="n">
-        <v>99285250</v>
+        <v>93688200</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="63">
@@ -2452,31 +2452,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>8760</v>
+        <v>288500</v>
       </c>
       <c r="F63" t="n">
-        <v>10695</v>
+        <v>152</v>
       </c>
       <c r="G63" t="n">
-        <v>93688200</v>
-      </c>
-      <c r="H63" t="n">
-        <v>6.31</v>
-      </c>
+        <v>43852000</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2486,29 +2484,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>휴메딕스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>200670</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>288500</v>
+        <v>25850</v>
       </c>
       <c r="F64" t="n">
-        <v>152</v>
+        <v>3824</v>
       </c>
       <c r="G64" t="n">
-        <v>43852000</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>98850400</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.15</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>휴메딕스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>200670</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2532,16 +2532,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>25850</v>
+        <v>386500</v>
       </c>
       <c r="F65" t="n">
-        <v>3824</v>
+        <v>234</v>
       </c>
       <c r="G65" t="n">
-        <v>98850400</v>
+        <v>90441000</v>
       </c>
       <c r="H65" t="n">
-        <v>1.15</v>
+        <v>-9.27</v>
       </c>
     </row>
     <row r="66">
@@ -2552,31 +2552,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>386500</v>
+        <v>60400</v>
       </c>
       <c r="F66" t="n">
-        <v>234</v>
+        <v>1657</v>
       </c>
       <c r="G66" t="n">
-        <v>90441000</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-9.27</v>
-      </c>
+        <v>100082800</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2586,12 +2584,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>226950</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2600,13 +2598,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>60400</v>
+        <v>95900</v>
       </c>
       <c r="F67" t="n">
-        <v>1657</v>
+        <v>1044</v>
       </c>
       <c r="G67" t="n">
-        <v>100082800</v>
+        <v>100119600</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2618,27 +2616,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>226950</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>95900</v>
+        <v>101200</v>
       </c>
       <c r="F68" t="n">
-        <v>1044</v>
+        <v>39</v>
       </c>
       <c r="G68" t="n">
-        <v>100119600</v>
+        <v>3946800</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2650,27 +2648,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>101200</v>
+        <v>114800</v>
       </c>
       <c r="F69" t="n">
-        <v>39</v>
+        <v>872</v>
       </c>
       <c r="G69" t="n">
-        <v>3946800</v>
+        <v>100105600</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2682,27 +2680,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>114800</v>
+        <v>48000</v>
       </c>
       <c r="F70" t="n">
-        <v>872</v>
+        <v>682</v>
       </c>
       <c r="G70" t="n">
-        <v>100105600</v>
+        <v>32736000</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2714,29 +2712,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>48000</v>
+        <v>126500</v>
       </c>
       <c r="F71" t="n">
-        <v>682</v>
+        <v>783</v>
       </c>
       <c r="G71" t="n">
-        <v>32736000</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>99049500</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.9399999999999999</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2746,31 +2746,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>328130</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>126500</v>
+        <v>9000</v>
       </c>
       <c r="F72" t="n">
-        <v>783</v>
+        <v>11124</v>
       </c>
       <c r="G72" t="n">
-        <v>99049500</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+        <v>100116000</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2780,29 +2778,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>425420</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>9000</v>
+        <v>52700</v>
       </c>
       <c r="F73" t="n">
-        <v>11124</v>
+        <v>2162</v>
       </c>
       <c r="G73" t="n">
-        <v>100116000</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>113937400</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-13.95</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2812,31 +2812,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>마녀공장</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>425420</t>
+          <t>439090</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>52700</v>
+        <v>16010</v>
       </c>
       <c r="F74" t="n">
-        <v>2162</v>
+        <v>6253</v>
       </c>
       <c r="G74" t="n">
-        <v>113937400</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-13.95</v>
-      </c>
+        <v>100110530</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2846,27 +2844,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>마녀공장</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>439090</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>16010</v>
+        <v>9350</v>
       </c>
       <c r="F75" t="n">
-        <v>6253</v>
+        <v>655</v>
       </c>
       <c r="G75" t="n">
-        <v>100110530</v>
+        <v>6124250</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2878,44 +2876,44 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>475830</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>9350</v>
+        <v>55900</v>
       </c>
       <c r="F76" t="n">
-        <v>655</v>
+        <v>1791</v>
       </c>
       <c r="G76" t="n">
-        <v>6124250</v>
+        <v>100116900</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>475830</t>
+          <t>032820</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2924,13 +2922,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>55900</v>
+        <v>11600</v>
       </c>
       <c r="F77" t="n">
-        <v>1791</v>
+        <v>8620</v>
       </c>
       <c r="G77" t="n">
-        <v>100116900</v>
+        <v>99992000</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2942,27 +2940,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>11600</v>
+        <v>18020</v>
       </c>
       <c r="F78" t="n">
-        <v>8620</v>
+        <v>5549</v>
       </c>
       <c r="G78" t="n">
-        <v>99992000</v>
+        <v>99992980</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2974,27 +2972,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>18020</v>
+        <v>93300</v>
       </c>
       <c r="F79" t="n">
-        <v>5549</v>
+        <v>1071</v>
       </c>
       <c r="G79" t="n">
-        <v>99992980</v>
+        <v>99924300</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -3006,12 +3004,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3020,13 +3018,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>93300</v>
+        <v>35550</v>
       </c>
       <c r="F80" t="n">
-        <v>1071</v>
+        <v>2812</v>
       </c>
       <c r="G80" t="n">
-        <v>99924300</v>
+        <v>99966600</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3038,12 +3036,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3052,13 +3050,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>35550</v>
+        <v>62800</v>
       </c>
       <c r="F81" t="n">
-        <v>2812</v>
+        <v>1592</v>
       </c>
       <c r="G81" t="n">
-        <v>99966600</v>
+        <v>99977600</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3070,27 +3068,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>62800</v>
+        <v>10920</v>
       </c>
       <c r="F82" t="n">
-        <v>1592</v>
+        <v>9157</v>
       </c>
       <c r="G82" t="n">
-        <v>99977600</v>
+        <v>99994440</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3102,12 +3100,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3116,13 +3114,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>10920</v>
+        <v>22250</v>
       </c>
       <c r="F83" t="n">
-        <v>9157</v>
+        <v>6741</v>
       </c>
       <c r="G83" t="n">
-        <v>99994440</v>
+        <v>149987250</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3134,12 +3132,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3148,13 +3146,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>22250</v>
+        <v>23450</v>
       </c>
       <c r="F84" t="n">
-        <v>6741</v>
+        <v>4264</v>
       </c>
       <c r="G84" t="n">
-        <v>149987250</v>
+        <v>99990800</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3166,27 +3164,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>23450</v>
+        <v>56500</v>
       </c>
       <c r="F85" t="n">
-        <v>4264</v>
+        <v>1769</v>
       </c>
       <c r="G85" t="n">
-        <v>99990800</v>
+        <v>99948500</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3198,27 +3196,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>56500</v>
+        <v>33600</v>
       </c>
       <c r="F86" t="n">
-        <v>1769</v>
+        <v>1488</v>
       </c>
       <c r="G86" t="n">
-        <v>99948500</v>
+        <v>49996800</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3230,27 +3228,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>33600</v>
+        <v>35900</v>
       </c>
       <c r="F87" t="n">
-        <v>1488</v>
+        <v>2785</v>
       </c>
       <c r="G87" t="n">
-        <v>49996800</v>
+        <v>99981500</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3262,12 +3260,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3276,13 +3274,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>35900</v>
+        <v>9350</v>
       </c>
       <c r="F88" t="n">
-        <v>2785</v>
+        <v>10695</v>
       </c>
       <c r="G88" t="n">
-        <v>99981500</v>
+        <v>99998250</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3294,27 +3292,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>9350</v>
+        <v>307500</v>
       </c>
       <c r="F89" t="n">
-        <v>10695</v>
+        <v>325</v>
       </c>
       <c r="G89" t="n">
-        <v>99998250</v>
+        <v>99937500</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3326,27 +3324,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>휴메딕스</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>200670</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>307500</v>
+        <v>26150</v>
       </c>
       <c r="F90" t="n">
-        <v>325</v>
+        <v>3824</v>
       </c>
       <c r="G90" t="n">
-        <v>99937500</v>
+        <v>99997600</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3358,27 +3356,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>휴메딕스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>200670</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>26150</v>
+        <v>426000</v>
       </c>
       <c r="F91" t="n">
-        <v>3824</v>
+        <v>234</v>
       </c>
       <c r="G91" t="n">
-        <v>99997600</v>
+        <v>99684000</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3390,12 +3388,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3404,13 +3402,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>426000</v>
+        <v>105200</v>
       </c>
       <c r="F92" t="n">
-        <v>234</v>
+        <v>950</v>
       </c>
       <c r="G92" t="n">
-        <v>99684000</v>
+        <v>99940000</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3422,12 +3420,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3436,13 +3434,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>105200</v>
+        <v>54200</v>
       </c>
       <c r="F93" t="n">
-        <v>950</v>
+        <v>2767</v>
       </c>
       <c r="G93" t="n">
-        <v>99940000</v>
+        <v>149971400</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3454,27 +3452,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편입(숏)</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>54200</v>
+        <v>127700</v>
       </c>
       <c r="F94" t="n">
-        <v>2767</v>
+        <v>783</v>
       </c>
       <c r="G94" t="n">
-        <v>149971400</v>
+        <v>99989100</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3486,12 +3484,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>425420</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3500,13 +3498,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>127700</v>
+        <v>46250</v>
       </c>
       <c r="F95" t="n">
-        <v>783</v>
+        <v>2162</v>
       </c>
       <c r="G95" t="n">
-        <v>99989100</v>
+        <v>99992500</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3518,61 +3516,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>425420</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>46250</v>
+        <v>8320</v>
       </c>
       <c r="F96" t="n">
-        <v>2162</v>
+        <v>6009</v>
       </c>
       <c r="G96" t="n">
-        <v>99992500</v>
+        <v>49994880</v>
       </c>
       <c r="H96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>파인엠텍</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>441270</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>8320</v>
-      </c>
-      <c r="F97" t="n">
-        <v>6009</v>
-      </c>
-      <c r="G97" t="n">
-        <v>49994880</v>
-      </c>
-      <c r="H97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
